--- a/emergency_report_forms/009_marina_boat_collision_incident_report_form--emergency_report_forms.xlsx
+++ b/emergency_report_forms/009_marina_boat_collision_incident_report_form--emergency_report_forms.xlsx
@@ -1,15 +1,15 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
-<workbook xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <workbookPr/>
   <workbookProtection/>
   <bookViews>
     <workbookView visibility="visible" minimized="0" showHorizontalScroll="1" showVerticalScroll="1" showSheetTabs="1" tabRatio="600" firstSheet="0" activeTab="0" autoFilterDateGrouping="1"/>
   </bookViews>
   <sheets>
-    <sheet name="survey" sheetId="1" state="visible" r:id="rId1"/>
-    <sheet name="choices" sheetId="2" state="visible" r:id="rId2"/>
-    <sheet name="settings" sheetId="3" state="visible" r:id="rId3"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="survey" sheetId="1" state="visible" r:id="rId1"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="choices" sheetId="2" state="visible" r:id="rId2"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="settings" sheetId="3" state="visible" r:id="rId3"/>
   </sheets>
   <definedNames/>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
@@ -918,8 +918,8 @@
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="24" customWidth="1" min="1" max="1"/>
-    <col width="50" customWidth="1" min="2" max="2"/>
-    <col width="50" customWidth="1" min="3" max="3"/>
+    <col width="11" customWidth="1" min="2" max="2"/>
+    <col width="11" customWidth="1" min="3" max="3"/>
   </cols>
   <sheetData>
     <row r="1">
@@ -947,12 +947,12 @@
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>{'id':_1,_'name':_'sail',_'label':_'sail'}</t>
+          <t>sail</t>
         </is>
       </c>
       <c r="C2" t="inlineStr">
         <is>
-          <t>{'id': 1, 'name': 'sail', 'label': 'Sail'}</t>
+          <t>Sail</t>
         </is>
       </c>
     </row>
@@ -964,12 +964,12 @@
       </c>
       <c r="B3" t="inlineStr">
         <is>
-          <t>{'id':_2,_'name':_'motor',_'label':_'motor'}</t>
+          <t>motor</t>
         </is>
       </c>
       <c r="C3" t="inlineStr">
         <is>
-          <t>{'id': 2, 'name': 'motor', 'label': 'Motor'}</t>
+          <t>Motor</t>
         </is>
       </c>
     </row>
@@ -981,12 +981,12 @@
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>{'id':_3,_'name':_'other',_'label':_'other'}</t>
+          <t>other</t>
         </is>
       </c>
       <c r="C4" t="inlineStr">
         <is>
-          <t>{'id': 3, 'name': 'other', 'label': 'Other'}</t>
+          <t>Other</t>
         </is>
       </c>
     </row>
@@ -998,12 +998,12 @@
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>{'id':_1,_'name':_'red',_'label':_'red'}</t>
+          <t>red</t>
         </is>
       </c>
       <c r="C5" t="inlineStr">
         <is>
-          <t>{'id': 1, 'name': 'red', 'label': 'Red'}</t>
+          <t>Red</t>
         </is>
       </c>
     </row>
@@ -1015,12 +1015,12 @@
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>{'id':_2,_'name':_'blue',_'label':_'blue'}</t>
+          <t>blue</t>
         </is>
       </c>
       <c r="C6" t="inlineStr">
         <is>
-          <t>{'id': 2, 'name': 'blue', 'label': 'Blue'}</t>
+          <t>Blue</t>
         </is>
       </c>
     </row>
@@ -1032,12 +1032,12 @@
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>{'id':_3,_'name':_'green',_'label':_'green'}</t>
+          <t>green</t>
         </is>
       </c>
       <c r="C7" t="inlineStr">
         <is>
-          <t>{'id': 3, 'name': 'green', 'label': 'Green'}</t>
+          <t>Green</t>
         </is>
       </c>
     </row>
@@ -1049,12 +1049,12 @@
       </c>
       <c r="B8" t="inlineStr">
         <is>
-          <t>{'id':_1,_'name':_'grounding',_'label':_'grounding'}</t>
+          <t>grounding</t>
         </is>
       </c>
       <c r="C8" t="inlineStr">
         <is>
-          <t>{'id': 1, 'name': 'grounding', 'label': 'Grounding'}</t>
+          <t>Grounding</t>
         </is>
       </c>
     </row>
@@ -1066,12 +1066,12 @@
       </c>
       <c r="B9" t="inlineStr">
         <is>
-          <t>{'id':_2,_'name':_'contact',_'label':_'contact'}</t>
+          <t>contact</t>
         </is>
       </c>
       <c r="C9" t="inlineStr">
         <is>
-          <t>{'id': 2, 'name': 'contact', 'label': 'Contact'}</t>
+          <t>Contact</t>
         </is>
       </c>
     </row>
